--- a/resources/Import-Lieferungen.xlsx
+++ b/resources/Import-Lieferungen.xlsx
@@ -1,168 +1,444 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\digiflux\digiflux-transactions\digiflux-transaction\src\main\resources\import-templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\projects\digiflux\digiflux-transactions\digiflux-transaction\src\main\resources\import-templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB6D2391-4B34-4132-9E31-F04E083764E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAB1E687-9686-4420-9D33-2FB403589165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="-120" windowWidth="27750" windowHeight="16440" xr2:uid="{273090FA-453D-418B-8531-ADA3887B00B5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C32E4A49-B866-4A18-9572-904E834AD043}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Liefermeldungen" sheetId="1" r:id="rId1"/>
+    <sheet name="Referenzdaten" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="129">
+  <si>
+    <t>Abgeberstandort-ID</t>
+  </si>
+  <si>
+    <t>Abgeberstandort-ID Quellsystem</t>
+  </si>
+  <si>
+    <t>Empfängerstandort-ID</t>
+  </si>
+  <si>
+    <t>Empfängerstandort-ID Quellsystem</t>
+  </si>
+  <si>
+    <t>Produkt-ID</t>
+  </si>
+  <si>
+    <t>Produkt-ID Quellsystem</t>
+  </si>
+  <si>
+    <t>Produktfamilie</t>
+  </si>
+  <si>
+    <t>Menge</t>
+  </si>
+  <si>
+    <t>Einheit</t>
+  </si>
   <si>
     <t>Lieferdatum</t>
   </si>
   <si>
-    <t>Liefer-Nr. Kassensystem</t>
-  </si>
-  <si>
-    <t>Kommentar</t>
-  </si>
-  <si>
-    <t>Produkt-ID</t>
-  </si>
-  <si>
-    <t>Backup Vorname</t>
-  </si>
-  <si>
-    <t>Backup Postleitzahl</t>
-  </si>
-  <si>
-    <t>Backup Kanton</t>
-  </si>
-  <si>
-    <t>Backup Ort</t>
-  </si>
-  <si>
-    <t>Backup Geburtsdatum</t>
-  </si>
-  <si>
-    <t>Backup Nachname</t>
-  </si>
-  <si>
-    <t>Menge</t>
-  </si>
-  <si>
-    <t>Einheit</t>
-  </si>
-  <si>
-    <t>Name Kassensystem</t>
-  </si>
-  <si>
-    <t>Typ Abgeber Vorrat</t>
-  </si>
-  <si>
-    <t>Typ Empfänger Vorrat</t>
-  </si>
-  <si>
-    <t>ID Abgeber Vorrat</t>
-  </si>
-  <si>
-    <t>ID Empfänger Vorrat</t>
-  </si>
-  <si>
-    <t>Backup</t>
-  </si>
-  <si>
-    <t>Backup Telefon</t>
-  </si>
-  <si>
-    <t>Backup E-Mail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vorname Abgeber Vorrat </t>
-  </si>
-  <si>
-    <t>Nachname Abgeber Vorrat</t>
-  </si>
-  <si>
-    <t>Firmenname Abgeber Vorrat</t>
-  </si>
-  <si>
-    <t>Straße Abgeber Vorrat</t>
-  </si>
-  <si>
-    <t>Hausnummer Abgeber Vorrat</t>
-  </si>
-  <si>
-    <t>Postleitzahl Abgeber Vorrat</t>
-  </si>
-  <si>
-    <t>Stadt Abgeber Vorrat</t>
-  </si>
-  <si>
-    <t>Land Abgeber Vorrat</t>
-  </si>
-  <si>
-    <t>Kanton Abgeber Vorrat</t>
-  </si>
-  <si>
-    <t>Telefonnummer Abgeber Vorrat</t>
-  </si>
-  <si>
-    <t>E-Mail Abgeber Vorrat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vorname Empfänger Vorrat </t>
-  </si>
-  <si>
-    <t>Nachname Empfänger Vorrat</t>
-  </si>
-  <si>
-    <t>Firmenname Empfänger Vorrat</t>
-  </si>
-  <si>
-    <t>Straße Empfänger Vorrat</t>
-  </si>
-  <si>
-    <t>Hausnummer Empfänger Vorrat</t>
-  </si>
-  <si>
-    <t>Postleitzahl Empfänger Vorrat</t>
-  </si>
-  <si>
-    <t>Stadt Empfänger Vorrat</t>
-  </si>
-  <si>
-    <t>Land Empfänger Vorrat</t>
-  </si>
-  <si>
-    <t>Kanton Empfänger Vorrat</t>
-  </si>
-  <si>
-    <t>Telefonnummer Empfänger Vorrat</t>
-  </si>
-  <si>
-    <t>E-Mail Empfänger Vorrat</t>
+    <t>Lieferschein-Nr</t>
+  </si>
+  <si>
+    <t>Kommentar / Retournierungsgrund / Stonierungsgrund</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abgeber Vorname </t>
+  </si>
+  <si>
+    <t>Abgeber Nachname</t>
+  </si>
+  <si>
+    <t>Abgeber Firmenname</t>
+  </si>
+  <si>
+    <t>Abgeber Strasse</t>
+  </si>
+  <si>
+    <t>Abgeber Hausnummer</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Abgeber PLZ *</t>
+  </si>
+  <si>
+    <t>Abgeber Ort *</t>
+  </si>
+  <si>
+    <t>Abgeber Kanton</t>
+  </si>
+  <si>
+    <t>Abgeber Land</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empfänger Vorname </t>
+  </si>
+  <si>
+    <t>Empfänger Nachname</t>
+  </si>
+  <si>
+    <t>Empfänger Firmenname</t>
+  </si>
+  <si>
+    <t>Empfänger Strasse</t>
+  </si>
+  <si>
+    <t>Empfänger Hausnummer</t>
+  </si>
+  <si>
+    <t>Empfänger Land</t>
+  </si>
+  <si>
+    <t>Empfänger Kanton</t>
+  </si>
+  <si>
+    <t>Empfänger Tel</t>
+  </si>
+  <si>
+    <t>Stellvertreter Vorname *</t>
+  </si>
+  <si>
+    <t>Stellvertreter Nachname *</t>
+  </si>
+  <si>
+    <t>Stellvertreter Kanton</t>
+  </si>
+  <si>
+    <t>Stellvertreter Tel</t>
+  </si>
+  <si>
+    <t>Art der Korrekturlieferung</t>
+  </si>
+  <si>
+    <t>Betroffene Lieferung-ID</t>
+  </si>
+  <si>
+    <t>Betroffene Lieferung-ID Quellsystem</t>
+  </si>
+  <si>
+    <t>shippedFromStock.id</t>
+  </si>
+  <si>
+    <t>shippedFromStock.sourceSystemId</t>
+  </si>
+  <si>
+    <t>shippedToStock.id</t>
+  </si>
+  <si>
+    <t>shippedToStock.sourceSystemId</t>
+  </si>
+  <si>
+    <t>product.id</t>
+  </si>
+  <si>
+    <t>product.sourceSystemId</t>
+  </si>
+  <si>
+    <t>productfamily</t>
+  </si>
+  <si>
+    <t>quantity.amount</t>
+  </si>
+  <si>
+    <t>quantity.unit</t>
+  </si>
+  <si>
+    <t>shipmentDate</t>
+  </si>
+  <si>
+    <t>alternateId.sourceSystemId</t>
+  </si>
+  <si>
+    <t>deliveryNumber</t>
+  </si>
+  <si>
+    <t>comment</t>
+  </si>
+  <si>
+    <t>shippedFromAddress.firstName</t>
+  </si>
+  <si>
+    <t>shippedFromAddress.lastName</t>
+  </si>
+  <si>
+    <t>shippedFromAddress.organisationName</t>
+  </si>
+  <si>
+    <t>shippedFromAddress.street</t>
+  </si>
+  <si>
+    <t>shippedFromAddress.houseNumber</t>
+  </si>
+  <si>
+    <t>shippedFromAddress.zipCode</t>
+  </si>
+  <si>
+    <t>shippedFromAddress.town</t>
+  </si>
+  <si>
+    <t>shippedFromAddress.canton</t>
+  </si>
+  <si>
+    <t>shippedFromAddress.country</t>
+  </si>
+  <si>
+    <t>shippedFromAddress.phoneNumber</t>
+  </si>
+  <si>
+    <t>shippedFromAddress.emailAddress</t>
+  </si>
+  <si>
+    <t>shippedToAddress.firstName</t>
+  </si>
+  <si>
+    <t>shippedToAddress.lastName</t>
+  </si>
+  <si>
+    <t>shippedToAddress.organisationName</t>
+  </si>
+  <si>
+    <t>shippedToAddress.street</t>
+  </si>
+  <si>
+    <t>shippedToAddress.houseNumber</t>
+  </si>
+  <si>
+    <t>shippedToAddress.zipCode</t>
+  </si>
+  <si>
+    <t>shippedToAddress.town</t>
+  </si>
+  <si>
+    <t>shippedToAddress.canton</t>
+  </si>
+  <si>
+    <t>shippedToAddress.phoneNumber</t>
+  </si>
+  <si>
+    <t>shippedToAddress.emailAddress</t>
+  </si>
+  <si>
+    <t>specialDeliveryType</t>
+  </si>
+  <si>
+    <t>affectedDelivery.id</t>
+  </si>
+  <si>
+    <t>Einheiten</t>
+  </si>
+  <si>
+    <t>l</t>
+  </si>
+  <si>
+    <t>m3</t>
+  </si>
+  <si>
+    <t>kg</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>pc</t>
+  </si>
+  <si>
+    <t>DFLID</t>
+  </si>
+  <si>
+    <t>BUR</t>
+  </si>
+  <si>
+    <t>DIGIFLUX</t>
+  </si>
+  <si>
+    <t>AGATE</t>
+  </si>
+  <si>
+    <t>Quellsysteme Empfänger</t>
+  </si>
+  <si>
+    <t>Quellsysteme Produkte</t>
+  </si>
+  <si>
+    <t>INFOFITOZ</t>
+  </si>
+  <si>
+    <t>RPC</t>
+  </si>
+  <si>
+    <t>GTIN</t>
+  </si>
+  <si>
+    <t>UID</t>
+  </si>
+  <si>
+    <t>Produktfamilien</t>
+  </si>
+  <si>
+    <t>PLANT_PROTECTION_PRODUCT</t>
+  </si>
+  <si>
+    <t>FERTILISER</t>
+  </si>
+  <si>
+    <t>TRADE_PRODUCT</t>
+  </si>
+  <si>
+    <t>FEEDSTUFF</t>
+  </si>
+  <si>
+    <t>FARM_MANURE_RECYCLING</t>
+  </si>
+  <si>
+    <t>Quellsysteme Abgeber</t>
+  </si>
+  <si>
+    <t>proxyAddress.town</t>
+  </si>
+  <si>
+    <t>proxyAddress.firstName</t>
+  </si>
+  <si>
+    <t>proxyAddress.emailAddress</t>
+  </si>
+  <si>
+    <t>proxyAddress.swissZipCode</t>
+  </si>
+  <si>
+    <t>proxyAddress.canton</t>
+  </si>
+  <si>
+    <t>proxyAddress.phoneNumber</t>
+  </si>
+  <si>
+    <t>alternateid.id</t>
+  </si>
+  <si>
+    <t>shippedToAddress.country</t>
+  </si>
+  <si>
+    <t>proxyAddress.lastName</t>
+  </si>
+  <si>
+    <t>affectedDelivery.sourceSystemId</t>
+  </si>
+  <si>
+    <t>Spezial-Lieferarten</t>
+  </si>
+  <si>
+    <t>CANCELLATION</t>
+  </si>
+  <si>
+    <t>RETURN</t>
+  </si>
+  <si>
+    <t>eigene Liefer-ID</t>
+  </si>
+  <si>
+    <t>eigene Liefer-ID Quellsystem</t>
+  </si>
+  <si>
+    <t>Lieferant</t>
+  </si>
+  <si>
+    <t>supplierInfo.supplier</t>
+  </si>
+  <si>
+    <t>Name/Firma Lieferant</t>
+  </si>
+  <si>
+    <t>supplierInfo.name</t>
+  </si>
+  <si>
+    <t>E-Mail Lieferant</t>
+  </si>
+  <si>
+    <t>supplierInfo.mail</t>
+  </si>
+  <si>
+    <t>Telefonnummer Lieferant</t>
+  </si>
+  <si>
+    <t>supplierInfo.phone</t>
+  </si>
+  <si>
+    <t>TRANSPORTER</t>
+  </si>
+  <si>
+    <t>RECIPIENT</t>
+  </si>
+  <si>
+    <t>SENDER</t>
+  </si>
+  <si>
+    <t>Abgeber Tel</t>
+  </si>
+  <si>
+    <t>Stellvertreter E-Mail *</t>
+  </si>
+  <si>
+    <t>Stellvertreter PLZ *</t>
+  </si>
+  <si>
+    <t>Stellvertreter Ort *</t>
+  </si>
+  <si>
+    <t>Abgeber E-Mail *</t>
+  </si>
+  <si>
+    <t>Empfänger PLZ *</t>
+  </si>
+  <si>
+    <t>Empfänger Ort *</t>
+  </si>
+  <si>
+    <t>Empfänger E-Mail *</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-  </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -176,36 +452,185 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FF172B4D"/>
-      <name val="Segoe UI"/>
+      <color theme="0"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial Narrow"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E75B6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6699FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99CCFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCECFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3366FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCFF99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCFF66"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99CC00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -228,27 +653,416 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFB9B9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFB9B9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFFFCC"/>
+      <color rgb="FFFFFF99"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -576,189 +1390,581 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F8559B1-A3D2-4D04-B856-54A00BDC15FF}">
-  <dimension ref="A1:AP2"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97920AB7-C216-4C05-8203-837670747347}">
+  <dimension ref="A1:AX3"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.5703125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="12" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="88.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="16.140625" style="4" customWidth="1"/>
-    <col min="8" max="20" width="20.85546875" style="4" customWidth="1"/>
-    <col min="21" max="34" width="17.42578125" style="1" customWidth="1"/>
-    <col min="35" max="35" width="16.42578125" style="1" customWidth="1"/>
-    <col min="36" max="36" width="16.140625" style="1" customWidth="1"/>
-    <col min="37" max="37" width="20.140625" style="6" customWidth="1"/>
-    <col min="38" max="38" width="18.28515625" style="4" customWidth="1"/>
-    <col min="39" max="39" width="16.140625" style="4" customWidth="1"/>
-    <col min="40" max="40" width="15.5703125" style="4" customWidth="1"/>
-    <col min="41" max="42" width="14.28515625" style="4" customWidth="1"/>
-    <col min="43" max="16384" width="8.85546875" style="1"/>
+    <col min="1" max="1" width="16.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="44.25" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="24.375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="24.125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="31" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21.375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="27.75" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="23.25" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="20.625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="22.125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="22.625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="28" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="27.25" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="22.25" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="29" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="25.875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="21.375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="18.75" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="20.625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="26.125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="25.375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="20.375" bestFit="1" customWidth="1"/>
+    <col min="38" max="40" width="21.625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="15" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="22.375" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="19.625" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="30.125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="30.625" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="19.875" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="30.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:50" ht="15.75" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="L1" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="M1" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="O1" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H1" s="3" t="s">
+      <c r="P1" s="50" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q1" s="45" t="s">
+        <v>14</v>
+      </c>
+      <c r="R1" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1" s="7" t="s">
+      <c r="S1" s="47" t="s">
+        <v>16</v>
+      </c>
+      <c r="T1" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="U1" s="47" t="s">
+        <v>18</v>
+      </c>
+      <c r="V1" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="W1" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="X1" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y1" s="54" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z1" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="AA1" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="AB1" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="AC1" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="AD1" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="AE1" s="63" t="s">
+        <v>126</v>
+      </c>
+      <c r="AF1" s="63" t="s">
+        <v>127</v>
+      </c>
+      <c r="AG1" s="63" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH1" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="Q1" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="7" t="s">
+      <c r="AI1" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="S1" s="7" t="s">
+      <c r="AJ1" s="66" t="s">
+        <v>128</v>
+      </c>
+      <c r="AK1" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="T1" s="7" t="s">
+      <c r="AL1" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="U1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="W1" s="7" t="s">
+      <c r="AM1" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="AN1" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="AO1" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="AP1" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="X1" s="7" t="s">
+      <c r="AQ1" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="Y1" s="7" t="s">
+      <c r="AR1" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="Z1" s="7" t="s">
+      <c r="AS1" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="AA1" s="7" t="s">
+      <c r="AT1" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="AB1" s="7" t="s">
+      <c r="AU1" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="AV1" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AW1" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AX1" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:50" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="AC1" s="7" t="s">
+      <c r="B2" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="AD1" s="7" t="s">
+      <c r="C2" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="AE1" s="7" t="s">
+      <c r="D2" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="AF1" s="7" t="s">
+      <c r="E2" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="AG1" s="7" t="s">
+      <c r="F2" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="AH1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="AI1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AL1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="AM1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AO1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="AP1" s="3" t="s">
-        <v>18</v>
+      <c r="G2" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="I2" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="J2" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="K2" s="36" t="s">
+        <v>101</v>
+      </c>
+      <c r="L2" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="M2" s="37" t="s">
+        <v>47</v>
+      </c>
+      <c r="N2" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="O2" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="P2" s="52" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q2" s="46" t="s">
+        <v>51</v>
+      </c>
+      <c r="R2" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="S2" s="48" t="s">
+        <v>53</v>
+      </c>
+      <c r="T2" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="U2" s="48" t="s">
+        <v>55</v>
+      </c>
+      <c r="V2" s="48" t="s">
+        <v>56</v>
+      </c>
+      <c r="W2" s="48" t="s">
+        <v>57</v>
+      </c>
+      <c r="X2" s="55" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y2" s="56" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z2" s="59" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA2" s="60" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB2" s="62" t="s">
+        <v>62</v>
+      </c>
+      <c r="AC2" s="64" t="s">
+        <v>63</v>
+      </c>
+      <c r="AD2" s="64" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE2" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="AF2" s="64" t="s">
+        <v>66</v>
+      </c>
+      <c r="AG2" s="64" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH2" s="64" t="s">
+        <v>102</v>
+      </c>
+      <c r="AI2" s="67" t="s">
+        <v>68</v>
+      </c>
+      <c r="AJ2" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK2" s="39" t="s">
+        <v>96</v>
+      </c>
+      <c r="AL2" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="AM2" s="40" t="s">
+        <v>97</v>
+      </c>
+      <c r="AN2" s="40" t="s">
+        <v>98</v>
+      </c>
+      <c r="AO2" s="40" t="s">
+        <v>95</v>
+      </c>
+      <c r="AP2" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="AQ2" s="41" t="s">
+        <v>100</v>
+      </c>
+      <c r="AR2" s="42" t="s">
+        <v>70</v>
+      </c>
+      <c r="AS2" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="AT2" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="AU2" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="AV2" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="AW2" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="AX2" s="2" t="s">
+        <v>117</v>
       </c>
     </row>
-    <row r="2" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="C2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="4"/>
-      <c r="Z2" s="4"/>
-      <c r="AA2" s="4"/>
-      <c r="AB2" s="4"/>
-      <c r="AC2" s="4"/>
-      <c r="AD2" s="4"/>
-      <c r="AE2" s="4"/>
-      <c r="AF2" s="4"/>
-      <c r="AG2" s="4"/>
-      <c r="AH2" s="4"/>
-      <c r="AI2" s="4"/>
-      <c r="AJ2" s="4"/>
-      <c r="AK2" s="4"/>
+    <row r="3" spans="1:50" ht="15" thickTop="1" x14ac:dyDescent="0.2"/>
+  </sheetData>
+  <conditionalFormatting sqref="O1:Y2">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>$B1="DIGIFLUX"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z1:AJ2">
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>$D1="DIGIFLUX"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation showInputMessage="1" showErrorMessage="1" sqref="I1:I2" xr:uid="{41C41B0B-BB98-4E93-B98D-D6BE12469EAE}"/>
+    <dataValidation sqref="F1:F2" xr:uid="{CE1EFE85-E59D-4CA9-967F-91C225C4C417}"/>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="7">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0949DCBA-4CB8-49BB-B425-A59EEDECDD6E}">
+          <x14:formula1>
+            <xm:f>Referenzdaten!$A$2:$A$7</xm:f>
+          </x14:formula1>
+          <xm:sqref>B3:B1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0681EECF-0662-440C-8517-3EE869951CC5}">
+          <x14:formula1>
+            <xm:f>Referenzdaten!$B$2:$B$7</xm:f>
+          </x14:formula1>
+          <xm:sqref>D3:D1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" xr:uid="{B1602976-482E-4233-8EB9-0DD440AF6D6E}">
+          <x14:formula1>
+            <xm:f>Referenzdaten!$E$2:$E$6</xm:f>
+          </x14:formula1>
+          <xm:sqref>I3:I1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A959E36F-5AED-410E-9A74-BC24395A5940}">
+          <x14:formula1>
+            <xm:f>Referenzdaten!$D$2:$D$6</xm:f>
+          </x14:formula1>
+          <xm:sqref>G3:G1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" xr:uid="{6D2AFA59-EAC2-45B3-93D1-71228EEBDC14}">
+          <x14:formula1>
+            <xm:f>Referenzdaten!$C$2:$C$6</xm:f>
+          </x14:formula1>
+          <xm:sqref>F3:F1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4C600349-7FAB-4338-982B-B37BC9D41130}">
+          <x14:formula1>
+            <xm:f>Referenzdaten!$F$2:$F$4</xm:f>
+          </x14:formula1>
+          <xm:sqref>AR3:AR1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C81C0882-5ABF-4A41-B44D-5F0110ED021B}">
+          <x14:formula1>
+            <xm:f>Referenzdaten!$G$2:$G$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>AU3:AU1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1AFD879-5AFF-48CA-9336-EF8C8AD478BF}">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="21.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.625" customWidth="1"/>
+    <col min="6" max="6" width="18.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="F4" s="16"/>
+      <c r="G4" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="16"/>
+      <c r="B5" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="F5" s="16"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="16"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="F6" s="16"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010033727A32B53FDB439A7613C1EE7A0FB3" ma:contentTypeVersion="2" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3ed33107a6afa82f500c88ffd6245706">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3de2290d-d910-4383-a0bc-3b06847af7c8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d25e3766e4ed164c531f04906350fa66" ns2:_="">
-    <xsd:import namespace="3de2290d-d910-4383-a0bc-3b06847af7c8"/>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100471DD6559E55A546B074F23EA170A9D8" ma:contentTypeVersion="2" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="0ec5289131fe115a2bbc9c534010f8f4">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="518f7fb1-3ebb-4489-bdf2-db4c4a346966" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e2750b86e1cadb73e7aafa6492279334" ns2:_="">
+    <xsd:import namespace="518f7fb1-3ebb-4489-bdf2-db4c4a346966"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -774,10 +1980,10 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3de2290d-d910-4383-a0bc-3b06847af7c8" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="518f7fb1-3ebb-4489-bdf2-db4c4a346966" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Freigegeben für" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -796,7 +2002,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Freigegeben für - Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -813,8 +2019,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Inhaltstyp"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titel"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -903,12 +2109,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -919,13 +2119,29 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53295997-7751-4C6B-B821-BF9B62F6FFED}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB9544CE-2934-4384-98BB-708C537E5819}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="518f7fb1-3ebb-4489-bdf2-db4c4a346966"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48169C4-0F43-4389-A3D6-F6C06ABC8D92}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="3de2290d-d910-4383-a0bc-3b06847af7c8"/>
+    <ds:schemaRef ds:uri="518f7fb1-3ebb-4489-bdf2-db4c4a346966"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
@@ -936,17 +2152,8 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BEA42C21-B719-4067-8C5E-4B0215EA3559}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CBB9142-8C05-4CDE-8AF4-22CDD5826334}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81FA455E-F4F2-440C-B5AC-6B823002F326}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
